--- a/Result/profitability/3645.xlsx
+++ b/Result/profitability/3645.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.35125</v>
+        <v>0.3975</v>
       </c>
       <c r="N2" t="n">
-        <v>26.56</v>
+        <v>27.79625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0.27375</v>
+        <v>0.35875</v>
       </c>
       <c r="N3" t="n">
-        <v>24.10625</v>
+        <v>25.75125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>0.20625</v>
+        <v>0.275</v>
       </c>
       <c r="N4" t="n">
-        <v>20.52875</v>
+        <v>22.74125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2225</v>
+        <v>0.31</v>
       </c>
       <c r="N5" t="n">
-        <v>20.99875</v>
+        <v>22.37625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0.27875</v>
+        <v>0.3275</v>
       </c>
       <c r="N6" t="n">
-        <v>21.3175</v>
+        <v>23.2125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.86</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3275</v>
+        <v>0.36</v>
       </c>
       <c r="N7" t="n">
-        <v>22.915</v>
+        <v>23.99375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,13 +1279,13 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3225</v>
+        <v>0.3462500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>23.80875</v>
+        <v>24.41375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -9318,6 +9318,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>681</v>
+      </c>
+      <c r="D71" t="n">
+        <v>409</v>
+      </c>
+      <c r="E71" t="n">
+        <v>272</v>
+      </c>
+      <c r="F71" t="n">
+        <v>39.96</v>
+      </c>
+      <c r="G71" t="n">
+        <v>158</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>23.27%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>161</v>
+      </c>
+      <c r="K71" t="n">
+        <v>117</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="N71" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.2835820895522387</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>4.840000000000003</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.1378132118451025</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.3807878369039392</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
